--- a/artfynd/A 6657-2021 artfynd.xlsx
+++ b/artfynd/A 6657-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122866957</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
